--- a/02-casos-de-prueba.xlsx
+++ b/02-casos-de-prueba.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>RN-03</t>
+          <t>RF-28, RN-03</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">

--- a/02-casos-de-prueba.xlsx
+++ b/02-casos-de-prueba.xlsx
@@ -1305,14 +1305,14 @@
           <t>Tabla de decisión (R5)</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>Falla</t>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Pasa</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>BUG-002</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1563,14 +1563,14 @@
           <t>Conjetura de errores</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>Falla</t>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Pasa</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>BUG-003</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1822,14 +1822,14 @@
           <t>Valores límite</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>Falla</t>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>Bloqueado</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>BUG-004</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1887,14 +1887,14 @@
           <t>Transición de estados</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>Falla</t>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Bloqueado</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>BUG-005</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2340,14 +2340,14 @@
           <t>Particiones de equivalencia</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>Falla</t>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Pasa</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>BUG-007</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2792,14 +2792,14 @@
           <t>Valores límite</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>Falla</t>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Pasa</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>BUG-010</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">

--- a/02-casos-de-prueba.xlsx
+++ b/02-casos-de-prueba.xlsx
@@ -1887,9 +1887,9 @@
           <t>Transición de estados</t>
         </is>
       </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>Bloqueado</t>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Pasa</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
